--- a/ExcelTable/SlotMachine.xlsx
+++ b/ExcelTable/SlotMachine.xlsx
@@ -5279,7 +5279,7 @@
         <x:v>BIG_MATCH_SCREEN_SPRAY</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>49f7b6c23fc645e798f7ce0458b356bc</x:v>
+        <x:v>b21f6d1b6d8d4c5ebe36b6d5b4503553</x:v>
       </x:c>
       <x:c r="D5" s="16" t="n">
         <x:v>2</x:v>
